--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/LNB管理手順書_草案.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/LNB管理手順書_草案.xlsx
@@ -92,21 +92,21 @@
     </font>
     <font>
       <name val="游ゴシック"/>
-      <b val="1"/>
-      <color rgb="001F3864"/>
-      <sz val="11"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
     </font>
     <font>
       <name val="游ゴシック"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="游ゴシック"/>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="9"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="游ゴシック"/>
@@ -115,7 +115,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -125,11 +125,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -218,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -233,27 +228,30 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -642,7 +640,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="16.5" customHeight="1">
+    <row r="5" ht="17.5" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>文書名</t>
@@ -654,7 +652,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="16.5" customHeight="1">
+    <row r="6" ht="17.5" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>文書番号</t>
@@ -666,7 +664,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="16.5" customHeight="1">
+    <row r="7" ht="17.5" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>版</t>
@@ -674,11 +672,11 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>0.7(草案・未検証)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="16.5" customHeight="1">
+          <t>0.9(草案・未検証)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17.5" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>対象システム</t>
@@ -690,7 +688,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
+    <row r="9" ht="17.5" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>作成</t>
@@ -702,7 +700,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
+    <row r="10" ht="17.5" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>作成チームリーダー</t>
@@ -714,7 +712,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
+    <row r="11" ht="17.5" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>承認 / 検印</t>
@@ -726,7 +724,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
+    <row r="12" ht="17.5" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>作成日 / 承認日</t>
@@ -738,7 +736,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
+    <row r="13" ht="17.5" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>様式の参考</t>
@@ -750,7 +748,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
+    <row r="14" ht="17.5" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>文書状態</t>
@@ -762,7 +760,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
+    <row r="15" ht="17.5" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>認証情報</t>
@@ -788,8 +786,8 @@
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -798,15 +796,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -819,6 +819,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -833,127 +838,130 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>8. バックアップ</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>正式な保存先</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>要確認。DGS が経路に現れるが位置づけ未確認</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>取得者</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>取得時刻</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>世代数・保持期間</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>一括取得の可否</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>成否の確認者</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="43.5" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+    <row r="15"/>
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>ここが埋まっていないことが最大の危険。Pana-CIM と Eg-Pro では、バックアップ障害が2件とも「成否を確認する担当が決まっていなかった」ことで長期化している(Eg-Pro のサブサーバー同期は1年以上、nksv523 は6月から暫定運用のまま)。手順書を作るだけでは同じことが起きる。誰がどこで結果を確認し、失敗時に何をするかまで書くこと。</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="16" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="16.5" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>LNB の運用: DGS を介した手作業。ジョブを消す前に過去ジョブへエクスポートし、必要時にインポートして戻す。取得目的は特定できていない(慣習として続いている)。検討事項: Pana-CIM で一括取得できないか。保存は Pana-CIM で行う。確認担当: 篠原、大塚、茂木。</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="14" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -961,6 +969,9 @@
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A18:G18"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -975,8 +986,8 @@
   <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -985,15 +996,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -1006,6 +1019,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1020,96 +1038,101 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>9. 復旧</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>実施条件</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>手順</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>確認の頻度</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>記録様式</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+    <row r="13"/>
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>戻せることを確認していないバックアップは、バックアップではない。§8 が埋まったら、戻す試験を一度やってから本章を書く。</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="14" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A6:G6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1124,8 +1147,8 @@
   <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -1134,15 +1157,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -1155,6 +1180,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1169,20 +1199,21 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>10-1. 記載する事象</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
@@ -1193,237 +1224,243 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>10-2. 中断と連絡</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="14" t="n"/>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="16" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>欄</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>記載</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>異常を検知したときの最初の連絡先</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>連絡がつかない場合の次の連絡先</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>実施者がその場で行ってよい対応</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>実施者が行ってはいけない対応</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>点検を中断して連絡する条件</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>点検中にサービスが停止した場合の応急処置</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="19" ht="17.5" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>上記の参照先文書</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
+    <row r="20"/>
     <row r="21" ht="16.5" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>会議では、異常時の連絡先と復旧確認の実施条件を確認事項として挙げたまま結論に至っていない。</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="14" t="n"/>
-    </row>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="16" t="n"/>
+    </row>
+    <row r="22"/>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>10-3. ベンダーへの依頼</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="14" t="n"/>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="16" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25" ht="17.5" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>欄</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>記載</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="16" t="inlineStr">
+    <row r="26" ht="17.5" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>ベンダー名</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>パナソニック コネクト株式会社</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1">
-      <c r="A27" s="16" t="inlineStr">
+    <row r="27" ht="17.5" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>連絡先</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+    <row r="28" ht="17.5" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>依頼方法(電話・メール・システム)</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+    <row r="29" ht="17.5" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>保守契約の有無と対応時間帯</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="30" ht="17.5" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>自社で対応する範囲</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
+    <row r="31" ht="17.5" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>ベンダーへ依頼する範囲</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="18" t="inlineStr">
+    <row r="32"/>
+    <row r="33" ht="17.5" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>自社とベンダーの境界が決まっていないと、異常時に誰も動かない時間が生まれる。</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="14" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1433,6 +1470,9 @@
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1447,8 +1487,8 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -1457,15 +1497,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -1478,6 +1520,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1492,260 +1539,266 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>11. 記録の管理</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>現在の記録の残し方</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>要確認(紙・ファイル・システム)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>保存先</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>既存の様式</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>保存期間</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>記録票を本書に内包するか別紙にするか</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>本書では内包とした(§13)。別紙に分ける判断になれば切り出す</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>画面やコマンド出力の保存先</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>12. 変更と文書管理</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="16" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="19" ht="17.5" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>文書番号の付番規則</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="20" ht="17.5" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>文書の保管場所</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="21" ht="17.5" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>改訂の承認者</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="22" ht="17.5" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>改訂の見直し時期</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>暫定版を作成し運用しながら改訂する方針は確定。時期と頻度は未確定</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="43.5" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="23" ht="17.5" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>様式の拡張</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>操作の種別・取り消し可否・中断条件の3欄を ZZZ-90000 に追加できるかが未確認。できない場合は備考欄に書く</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="24" ht="17.5" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>図の形式</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>ZZZ-90000 へ登録できる図の形式が未確認</t>
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="14" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="16" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="17.5" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>期日</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+    <row r="29" ht="17.5" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>文書の登録</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2026-12-28(月)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="30" ht="17.5" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>トライアル開始</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2027-01-05(火)</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="18" t="inlineStr">
+    <row r="31"/>
+    <row r="32" ht="17.5" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>残り日数から逆算すると、聞き取りを先に片付けないと間に合わない。本書の空欄はすべて聞き取りで埋まるもので、文書作成の作業量ではなく聞き取りの段取りが律速。</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n"/>
-      <c r="C32" s="13" t="n"/>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
-      <c r="F32" s="13" t="n"/>
-      <c r="G32" s="14" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1754,6 +1807,9 @@
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A6:G6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -1768,25 +1824,27 @@
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -1799,6 +1857,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -1813,33 +1876,35 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>13-1. 日次チェックシート</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>点検項目が未確定なので、列名は仮である。§6 が埋まった時点で列を確定させる。</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="31" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>対象システム</t>
         </is>
@@ -1850,8 +1915,8 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>年月</t>
         </is>
@@ -1862,8 +1927,8 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
@@ -1874,110 +1939,114 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+    <row r="13"/>
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>異常の有無</t>
         </is>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr"/>
-      <c r="C15" s="4" t="inlineStr"/>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr"/>
-      <c r="C16" s="4" t="inlineStr"/>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr"/>
-      <c r="G16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+    </row>
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>…</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr"/>
-      <c r="C17" s="4" t="inlineStr"/>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr"/>
-    </row>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+    </row>
+    <row r="18"/>
     <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>ライン別に列を分けてある。接続先が3つあるので、1つにまとめると、どのラインが異常だったのかが残らない。</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="16" t="n"/>
+    </row>
+    <row r="20"/>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>記入方法</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
-      <c r="D21" s="13" t="n"/>
-      <c r="E21" s="13" t="n"/>
-      <c r="F21" s="13" t="n"/>
-      <c r="G21" s="14" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="16" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="71.5" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>各ラインの欄</t>
         </is>
@@ -1988,8 +2057,8 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+    <row r="24" ht="44.5" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>異常の有無</t>
         </is>
@@ -2000,8 +2069,8 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+    <row r="25" ht="71.5" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>原則</t>
         </is>
@@ -2019,6 +2088,9 @@
     <mergeCell ref="A19:G19"/>
     <mergeCell ref="A6:G6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -2033,25 +2105,27 @@
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -2064,6 +2138,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2078,334 +2157,346 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>13-2. 月次チェックシート</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>LNB に月次の作業があるかが未確認。枠だけ置く。</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>確認項目</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>同席者</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>(未確定)</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>(未確定)</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr"/>
-      <c r="C12" s="4" t="inlineStr"/>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-    </row>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13"/>
     <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Pana-CIM と同日に実施する場合は、順序を記録すること。LNB は Pana-CIM のデータを参照しているため、どちらを先に触ったかが後で問題になる。</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="14" t="n"/>
-    </row>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="16" t="n"/>
+    </row>
+    <row r="15"/>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>13-3. 異常・連絡の記録</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="n"/>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="16" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>時刻</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>ライン</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>画面・文言</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>接続状態</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>中断内容</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>連絡先/時刻</t>
         </is>
       </c>
-      <c r="G18" s="15" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>記録No.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="4" t="inlineStr"/>
-      <c r="B19" s="4" t="inlineStr"/>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20" ht="16.5" customHeight="1">
-      <c r="A20" s="4" t="inlineStr"/>
-      <c r="B20" s="4" t="inlineStr"/>
-      <c r="C20" s="4" t="inlineStr"/>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr"/>
-    </row>
+    <row r="19" ht="17.5" customHeight="1">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+    </row>
+    <row r="20" ht="17.5" customHeight="1">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+    </row>
+    <row r="21"/>
     <row r="22" ht="16.5" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>画面に出ていた文言をそのまま書く。言い換えると、同じ事象かどうかが後で判定できない。</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="14" t="n"/>
-    </row>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="16" t="n"/>
+    </row>
+    <row r="23"/>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>13-4. 変更・定期作業の記録</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="14" t="n"/>
-    </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="16" t="n"/>
+    </row>
+    <row r="25"/>
+    <row r="26" ht="17.5" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>いずれも承認が要る。承認者の記入が無い行は、実施していないものとして扱う。</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="14" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="16" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="17.5" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>対象ライン</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>承認者</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>結果・記録No.</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="29" ht="31" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>再起動(要承認)</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr"/>
-      <c r="C29" s="4" t="inlineStr"/>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30" ht="31" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>設定変更(要承認)</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr"/>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
-    </row>
-    <row r="31" ht="16.5" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31" ht="44.5" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>バックアップ/復旧(手順確定後)</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr"/>
-      <c r="C31" s="4" t="inlineStr"/>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
-    </row>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32"/>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="14" t="inlineStr">
         <is>
           <t>13-5. 聞き取り記録(本書を埋めるための作業用)</t>
         </is>
       </c>
-      <c r="B33" s="13" t="n"/>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
-      <c r="F33" s="13" t="n"/>
-      <c r="G33" s="14" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="16" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35" ht="16.5" customHeight="1">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>点検文書ではないが、§14 を消していくための欄として内包する。聞き取りは一度で終わらない。誰にいつ何を聞いたかが残っていないと、同じことを二度聞くか、聞いたつもりで抜ける。</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n"/>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
-      <c r="F35" s="13" t="n"/>
-      <c r="G35" s="14" t="n"/>
-    </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="16" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37" ht="17.5" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>確認した欄</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>確認日</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>確認した内容</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>記入者</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="4" t="inlineStr"/>
-      <c r="B38" s="4" t="inlineStr"/>
-      <c r="C38" s="4" t="inlineStr"/>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
-    </row>
-    <row r="39" ht="16.5" customHeight="1">
-      <c r="A39" s="4" t="inlineStr"/>
-      <c r="B39" s="4" t="inlineStr"/>
-      <c r="C39" s="4" t="inlineStr"/>
-      <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
+    <row r="38" ht="17.5" customHeight="1">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+    </row>
+    <row r="39" ht="17.5" customHeight="1">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2419,6 +2510,9 @@
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A33:G33"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -2433,25 +2527,27 @@
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -2464,6 +2560,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -2478,666 +2579,668 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>14. 要確認事項一覧</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>記入シートの M(未充足一覧)と対応する。埋まったらシート側にも日付を入れる。</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="57" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="31" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>LNB と iLNB の関係</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>2026-10-05 更新。本書の対象は承認済みの L1〜L3 端末と稼働 LNB ソフトに限定した。iLNB と同一とは断定していない。製品資料に現れる両者の関係が未確認</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>現行実施者、ベンダー</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>サーバの名称と台数</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>接続先3つが3サーバを意味するとは限らない</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>現行実施者</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>端末の名称と設置場所</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>台数も未確認</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>現行実施者</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>バージョン</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>製品情報画面で確認</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>現行実施者</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>L4以降の有無</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>第4オクテットの付番規則から推測したにとどまる</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>現行実施者</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>実際の連携先とデータの向き</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>E-Link・GEM・PLC の有効化状況</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>導入時の構成図、連携仕様書</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>自社対応とベンダー依頼の境界</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>契約内容と対応時間帯</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>保守契約の管理部署</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16.5" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>ベンダーの連絡先と依頼方法</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr"/>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>保守契約の管理部署</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="19" ht="17.5" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>点検の実施者・確認者・承認者</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr"/>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>作成チーム、管理責任者</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="20" ht="17.5" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>停止判断者の氏名</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>担当は確定済み。氏名の記入が未了</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>管理責任者</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="16.5" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="21" ht="17.5" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>頻度区分と実施時間帯</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>休日の扱いを含む</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>作成チームで協議</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="22" ht="17.5" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>稼働中に実施できない項目</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr"/>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>現行実施者</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="57" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="23" ht="31" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>点検項目そのもの</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>本書で最も大きい空欄。2026-10-05 に公式資料から LNB接続状態(無線スキャナーとの接続)を候補として1件入れた(§6 Step 1)。自社 L1〜L3 に同じ表示があるかは未確認。残りは聞き取り待ち</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>現行実施者への聞き取り</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="24" ht="17.5" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>判定基準</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>正常の基準と、異常とみなす状態の両方</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>実機の画面を見ながら</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="16.5" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="25" ht="17.5" customHeight="1">
+      <c r="A25" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>実施場所・実施端末</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>現地か遠隔か、OS とブラウザ</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>現行実施者</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="26" ht="17.5" customHeight="1">
+      <c r="A26" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>必要な権限</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr"/>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t>現行実施者</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="27" ht="17.5" customHeight="1">
+      <c r="A27" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>認証情報の保管場所</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>§15 を先に処理すること</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>管理責任者</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="16.5" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="28" ht="17.5" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>異常時の連絡経路と中断条件</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>§10-2 の全欄</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>管理責任者</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="29" ht="17.5" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>バックアップの全項目</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>保存先・取得者・時刻・世代・保持期間・成否の確認者</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>現行実施者、管理責任者</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="30" ht="17.5" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>復旧の手順と戻す試験</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr"/>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t>現行実施者</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="31" ht="17.5" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>DGS の位置づけ</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>管理範囲に含めるか、境界の箱として扱うか</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>管理責任者</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="16.5" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="32" ht="17.5" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>記録の残し方と保存先</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>保存期間、確認者と確認の時期</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>作成チームで協議</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="33" ht="17.5" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>様式の拡張可否</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>操作の種別・取り消し可否・中断条件の3欄</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>ZZZ-90000 の管理部署</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="34" ht="17.5" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>文書番号と保管場所</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>付番規則、改訂の承認者</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>ZZZ-90000 の管理部署</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="35" ht="17.5" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>既存の操作説明の所在</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>操作手順のページが存在するとの発言がある。作成者を特定できていない</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>会議参加者</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="36" ht="17.5" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>CIMC-SV の LNBマップ</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>ESXiホスト(172.25.253.45)に表示される。LNB の管理対象に含めるか</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>現行実施者</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="37" ht="17.5" customHeight="1">
+      <c r="A37" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Pana-CIM との作業順序</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>LNB は Pana-CIM を参照している。再起動の順序に制約があるか</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>現行実施者</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="57" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="38" ht="31" customHeight="1">
+      <c r="A38" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>部品照合設定</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>公式資料に「無線スキャナーで部品照合機能を使うには LNB設定の部品照合設定が必要」とある(付録A-2)。自社で有効にしているか、点検対象にするかが未確認</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>現行実施者</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="43.5" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="39" ht="17.5" customHeight="1">
+      <c r="A39" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>構成図の LNB との対応</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>公式資料の NPMライン構成図に「LNB(FAパソコン)」がある(付録A-3)。社内で LNB と呼ぶ対象がこれと同じかが未確認</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>現行実施者、ベンダー</t>
         </is>
@@ -3148,6 +3251,9 @@
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A6:G6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3162,8 +3268,8 @@
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -3172,15 +3278,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -3193,6 +3301,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3207,106 +3320,110 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>15. 申し送り(認証情報の扱い)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>本書の作成中に、放置できない状態が見つかった。LNB の接続用ショートカット3件に、利用者名とパスワードが URL のクエリとして平文で埋め込まれている。置き場は 11_USBミラー_E/buckup/15575/desktop/ の L1_LNB.url L2_LNB.url L3_LNB.url。値は本書に書かない。</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>事実</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>なぜ問題か</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>パスワードが URL のクエリ文字列にある</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>ブラウザの履歴・プロキシのログ・サーバーのアクセスログに、そのまま残る。見た人を特定できない</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>通信が HTTP(暗号化なし)</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>同じネットワーク上で読める。ポート8080で平文</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>3ラインとも同じ利用者名・同じパスワード</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>1つ漏れると3ライン全部に入れる。どのラインから操作されたかも区別できない</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>この写しが業務用保管庫に入っている</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>保管庫は Google Drive で同期している。社内の共有フォルダに置いたのとは別の経路に、もう1部ある</t>
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>先に決めること(§14 No.17 より先に処理する)</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="16" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3317,8 +3434,8 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="19" ht="17.5" customHeight="1">
+      <c r="A19" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3329,8 +3446,8 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="20" ht="17.5" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3341,8 +3458,8 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+    <row r="21" ht="17.5" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3353,18 +3470,19 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="16.5" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>こちらの判断で消していない。現物を消すと、現場でその経路しか知らない人が入れなくなる可能性がある。rules.md の削除は承認が必要という扱いにも合わせた。</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-      <c r="E23" s="13" t="n"/>
-      <c r="F23" s="13" t="n"/>
-      <c r="G23" s="14" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3373,6 +3491,9 @@
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A23:G23"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3387,8 +3508,8 @@
   <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -3397,15 +3518,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -3418,6 +3541,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3432,33 +3560,35 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>16. 部品照合に関する参照</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>点検項目ではない。設定の前提として記録しておく。公式資料の記載(付録A-2): 無線スキャナーで部品照合機能を使用するには、LNB設定の部品照合設定を行う必要があります。</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+    </row>
+    <row r="9"/>
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -3469,47 +3599,51 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>付録A 引用元の原文</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="14" t="n"/>
-    </row>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="16" t="n"/>
+    </row>
+    <row r="13"/>
     <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>改変せずに載せる。本文は読みやすさのために整えてあるので、食い違いがあれば本付録を正とする。</t>
         </is>
       </c>
-      <c r="B14" s="13" t="n"/>
-      <c r="C14" s="13" t="n"/>
-      <c r="D14" s="13" t="n"/>
-      <c r="E14" s="13" t="n"/>
-      <c r="F14" s="13" t="n"/>
-      <c r="G14" s="14" t="n"/>
-    </row>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="16" t="n"/>
+    </row>
+    <row r="15"/>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>A-1 LNB接続状態(PanaCIM-EE 材料照合(サーバー無しタイプ)N7201A670J06・PDF通し19頁)</t>
         </is>
       </c>
-      <c r="B16" s="13" t="n"/>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="14" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="16" t="n"/>
+    </row>
+    <row r="17"/>
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>原文</t>
         </is>
@@ -3520,21 +3654,23 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>A-2 部品照合設定(同上・PDF通し66頁)</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="14" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="16" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22" ht="17.5" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>原文</t>
         </is>
@@ -3545,34 +3681,37 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="16.5" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>上記は製品資料の引用であり、自社 L1〜L3 への適用、設定状態、点検項目を確定するものではない。</t>
         </is>
       </c>
-      <c r="B24" s="13" t="n"/>
-      <c r="C24" s="13" t="n"/>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
-      <c r="F24" s="13" t="n"/>
-      <c r="G24" s="14" t="n"/>
-    </row>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="16" t="n"/>
+    </row>
+    <row r="25"/>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="14" t="inlineStr">
         <is>
           <t>A-3 システム構成(PanaCIM-EE 外部インターフェース N7201A522J17・PDF通し11〜12頁)</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="14" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="16" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="17.5" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>原文</t>
         </is>
@@ -3583,8 +3722,8 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+    <row r="29" ht="17.5" customHeight="1">
+      <c r="A29" s="17" t="inlineStr">
         <is>
           <t>限界</t>
         </is>
@@ -3595,21 +3734,23 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="14" t="inlineStr">
         <is>
           <t>付録B 資料の確認範囲</t>
         </is>
       </c>
-      <c r="B31" s="13" t="n"/>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
-      <c r="F31" s="13" t="n"/>
-      <c r="G31" s="14" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="16" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33" ht="17.5" customHeight="1">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>確認したもの</t>
         </is>
@@ -3620,8 +3761,8 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+    <row r="34" ht="17.5" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>原則</t>
         </is>
@@ -3632,8 +3773,8 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+    <row r="35" ht="17.5" customHeight="1">
+      <c r="A35" s="17" t="inlineStr">
         <is>
           <t>確認できていないもの</t>
         </is>
@@ -3656,6 +3797,9 @@
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A26:G26"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -3705,187 +3849,211 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>項目名を選ぶと該当シートへ移動します。各シートの「目次へ」から戻れます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>1.</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>目的と適用範囲</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>2.</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>用語</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="8" ht="16" customHeight="1">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>3.</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>構成と管理情報</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="9" ht="16" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>管理体制</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>5.</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>日次点検</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>6.</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>定期管理</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>7.</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>バックアップ</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>8.</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>復旧</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>9.</t>
         </is>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>異常時の対応</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>10.</t>
         </is>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>記録と文書管理</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>11.</t>
         </is>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>チェックシート(日次)</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>12.</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>チェックシート(月次・異常時)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>13.</t>
         </is>
       </c>
-      <c r="B18" s="9" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>要確認事項一覧</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>14.</t>
         </is>
       </c>
-      <c r="B19" s="9" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>申し送り(認証情報)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>15.</t>
         </is>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>引用と部品照合</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3896,28 +4064,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -3930,6 +4100,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -3944,229 +4119,284 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>改訂履歴</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>版</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>改訂内容</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>作成</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>草案作成。記入シートの確定事項と、保管庫内から確認できた接続先を反映</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="43.5" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="31" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>公式資料から LNB接続状態と部品照合設定を反映。適用範囲を L1〜L3 端末へ限定し、iLNB との同一視をやめた。引用を付録へ移した</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="70.5" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="44.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>実機確認の新規事実を反映。LWS の存在（ラインごとに1台のGUI端末）、再起動2種（LNBシステム／PC自体）、設定情報の自動バックアップ機能（現状は未実施）、稼働率フォルダのバックアップ扱い（推定・大塚さん確認待ち）</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="111" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="71.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>LWS 画面キャプチャ3枚（LNBキャプチャ）から確定できる事実を反映。再起動ページの実際のボタン名（LNB再起動／LNB-PC電源OFF／LNB-PCリブート）、DGS＝172.25.253.10 が上位システムとして Pingチェックに表示、L1 の生産設備構成（L1NPM-1〜7・SP70-1）、設定情報バックアップ／リストアのメニュー存在、基板バーコードスキャナ3項目が赤表示。版番号の内部矛盾（表紙0.2と履歴0.3）を解消</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="57" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="31" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>人名・割り当てを会議記録と再突合。§5 に副管理責任者（倉林筆頭・石井・茂木（絵））の行と「人名と割り当ての対応」を追加。停止判断者の記入待ち先を明記。§14 No.39 追加</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="57" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14" ht="44.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>人名・割り当てを本人確認により確定。§5 を改訂（管理責任者＝茂木（由）・倉林の2名体制、副管理責任者＝石井・茂木（絵））。茂木（絵）のスケジュール管理担当を明記。§14 No.39 解決</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="43.5" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="31" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>版管理の方針を明記（§12）。本書はベータ版（V1未満）であり、正式な版管理は運用開始後に実施する。運用開始（実装）時点で本改訂履歴は削除する予定</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44.5" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>稼働率フォルダの中身を実物（20260814-1L.htm）で確認。ラインごとの稼働率データ（期間・ロット一覧・仕損率・1〜7台目の稼働情報）であることを確定し、「LNB では保持できない情報」の根拠に据えた。大塚さんへの確認依頼を取り下げ（§14 No.32 解決）</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>篠原</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44.5" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>報告準備。§4-4 に図の読み方（種別ラベル・凡例）と PLM 閲覧問題の現状（大塚さん対応中・解決後に図解を拡充）を追記。構成図に種別ラベル・凡例・稼働率フォルダ（実物確認済み）を反映し視認性を改善</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>篠原</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>未</t>
         </is>
@@ -4176,6 +4406,9 @@
   <mergeCells count="1">
     <mergeCell ref="A6:G6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4190,8 +4423,8 @@
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -4200,15 +4433,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -4221,6 +4456,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4235,20 +4475,21 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>1. 目的</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -4259,21 +4500,23 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>2. 適用範囲</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="14" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="16" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>対象</t>
         </is>
@@ -4284,8 +4527,8 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>分冊</t>
         </is>
@@ -4296,8 +4539,8 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>分担</t>
         </is>
@@ -4308,8 +4551,8 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>環境</t>
         </is>
@@ -4320,8 +4563,8 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>未検証</t>
         </is>
@@ -4332,34 +4575,37 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>2-1. 背景(要約)</t>
         </is>
       </c>
-      <c r="B18" s="13" t="n"/>
-      <c r="C18" s="13" t="n"/>
-      <c r="D18" s="13" t="n"/>
-      <c r="E18" s="13" t="n"/>
-      <c r="F18" s="13" t="n"/>
-      <c r="G18" s="14" t="n"/>
-    </row>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="16" t="n"/>
+    </row>
+    <row r="19"/>
     <row r="20" ht="16.5" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>詳細は「LNB・Pana-CIM_管理文書作成_会議記録_追補.md」を参照。本章には経緯の詳細を書かない。</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n"/>
-      <c r="C20" s="13" t="n"/>
-      <c r="D20" s="13" t="n"/>
-      <c r="E20" s="13" t="n"/>
-      <c r="F20" s="13" t="n"/>
-      <c r="G20" s="14" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="16" t="n"/>
+    </row>
+    <row r="21"/>
+    <row r="22" ht="17.5" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>経緯</t>
         </is>
@@ -4370,8 +4616,8 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+    <row r="23" ht="17.5" customHeight="1">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>教訓</t>
         </is>
@@ -4382,18 +4628,19 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
+    <row r="24"/>
+    <row r="25" ht="16.5" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>本書は LNB_点検文書_情報記入シート.md の記入済み範囲だけで組んだ草案である。同シートの F(点検項目)は全行が空欄。点検の基準を推測で埋めていない。判定基準を創作すると、異常を正常と読む文書になる。</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
-      <c r="D25" s="13" t="n"/>
-      <c r="E25" s="13" t="n"/>
-      <c r="F25" s="13" t="n"/>
-      <c r="G25" s="14" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="16" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4403,6 +4650,9 @@
     <mergeCell ref="A25:G25"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4417,8 +4667,8 @@
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -4427,15 +4677,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -4448,6 +4700,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4462,145 +4719,146 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>3. 用語</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>語</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>意味</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="43.5" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>LNB</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>社内での呼び名。本書では、承認済みの L1〜L3 端末と、そこで稼働する LNB ソフトを対象とする。iLNB と同一であるとは断定しない</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="43.5" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>iLNB</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>統合ライン管理システム。メーカー公開資料での製品名。社内で「LNB」と呼んでいるものが iLNB と同じかは確認できていない</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>LWS</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>LNB の画面を提供しているアプリケーションの経路名。接続先URLの /lws/ にあたる。正式な呼称は要確認</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>L1 / L2 / L3</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>ラインの区分。接続先がライン別に3つ存在することから、少なくとも3ラインが対象と判断できる(§4-2)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>E-Link</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>iLNB が製品仕様として備える情報入出力の機構。自社での有効化状況は未確認</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>GEM通信</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>設備と上位システムの間の標準的な通信規約。iLNB が対応を表明している。自社での使用有無は未確認</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>PLC通信</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>設備制御機器との通信。同上</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>DGS</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>LNB のバックアップ経路に現れる系。本書での位置づけは要確認</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>アンドン</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>ラインの状態を表示する装置</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="57" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>CIMC-SV</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Pana-CIM 側の再起動対象モニタ。ESXiホスト画面(172.25.253.45)のナビゲータに「LNBマップ」が表示されるため、LNB の構成確認の入口になりうる。ただし LNB の管理対象に含めるかは要確認</t>
         </is>
@@ -4610,6 +4868,9 @@
   <mergeCells count="1">
     <mergeCell ref="A6:G6"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -4624,9 +4885,9 @@
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -4634,15 +4895,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -4655,6 +4918,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -4669,320 +4937,328 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>4-1. 管理対象</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="31" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>システム名(正式名称)</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>iLNB(統合ライン管理システム)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>ソフトウェア</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>iLNB</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>バージョン</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>未指定。製品情報画面での確認が必要</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
+    <row r="12" ht="31" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>サーバ(名称・台数)</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>要確認。接続先が3つあることから3系統以上と推定されるが、サーバ台数と一致するとは限らない</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="13" ht="31" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>端末(名称・設置場所)</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>要確認。各ラインの端末に導入されているとの推定にとどまる</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>ベンダー</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>パナソニック コネクト株式会社</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="43.5" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="15" ht="31" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>他システムとの連携</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Pana-CIM のデータを参照。製品仕様としては E-Link・GEM通信・PLC通信に対応。実際の接続先とデータの向きは未確認</t>
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>4-2. 接続先</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="14" t="n"/>
-    </row>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="16" t="n"/>
+    </row>
+    <row r="18"/>
     <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>保管庫内の資料から確認できた範囲。11_USBミラー_E に残っていたデスクトップのショートカット3件(L1_LNB.url L2_LNB.url L3_LNB.url)から読み取った。</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="16" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="17.5" customHeight="1">
+      <c r="A21" t="inlineStr">
         <is>
           <t>ライン</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>接続先</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="16.5" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="22" ht="17.5" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>172.25.253.11 ポート 8080</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>/lws/Login.do</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="16.5" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="23" ht="17.5" customHeight="1">
+      <c r="A23" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>172.25.253.21 ポート 8080</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>/lws/Login.do</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="16.5" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="24" ht="17.5" customHeight="1">
+      <c r="A24" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>172.25.253.31 ポート 8080</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>/lws/Login.do</t>
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>第4オクテットが 11/21/31 と並んでおり、ラインごとに10ずつ繰り上がる付番と見える。L4以降が存在するかは要確認。</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
-      <c r="C26" s="13" t="n"/>
-      <c r="D26" s="13" t="n"/>
-      <c r="E26" s="13" t="n"/>
-      <c r="F26" s="13" t="n"/>
-      <c r="G26" s="14" t="n"/>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="16" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="17.5" customHeight="1">
+      <c r="A28" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="16.5" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
+    <row r="29" ht="17.5" customHeight="1">
+      <c r="A29" t="inlineStr">
         <is>
           <t>通信</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>HTTP(暗号化なし)。§15 参照</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="16.5" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
+    <row r="30" ht="31" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>使用するアカウント</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>別紙管理</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="16.5" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
+    <row r="31" ht="17.5" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>必要な権限</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
+    <row r="32" ht="31" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>認証情報の保管場所</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>要確認。現状はデスクトップのショートカットに埋め込まれている(§15)</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+    <row r="33" ht="17.5" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>実施場所</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>要確認。現地の端末か遠隔接続か</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
+    <row r="34" ht="31" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>実施端末の OS・ブラウザ</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>4-3. 相関図</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
-      <c r="E36" s="13" t="n"/>
-      <c r="F36" s="13" t="n"/>
-      <c r="G36" s="14" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="16" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38" ht="31" customHeight="1">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
@@ -4993,8 +5269,8 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+    <row r="39" ht="31" customHeight="1">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>更新方針</t>
         </is>
@@ -5013,6 +5289,9 @@
     <mergeCell ref="A26:G26"/>
     <mergeCell ref="A19:G19"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -5027,9 +5306,9 @@
   <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -5037,15 +5316,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -5058,6 +5339,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -5072,182 +5358,186 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>5. 管理体制と役割</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>役割</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>不在時の代行</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="16.5" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" t="inlineStr">
         <is>
           <t>管理責任者</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>茂木（由）、倉林（2名体制）</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>互いに代行。両者不在時は副管理責任者</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" t="inlineStr">
         <is>
           <t>副管理責任者</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>石井、茂木（絵）（2名体制）</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>管理責任者不在時に代行</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="16.5" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11" ht="17.5" customHeight="1">
+      <c r="A11" t="inlineStr">
         <is>
           <t>点検の実施者</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" t="inlineStr">
         <is>
           <t>記録の確認者</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="16.5" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="13" ht="17.5" customHeight="1">
+      <c r="A13" t="inlineStr">
         <is>
           <t>文書の承認者</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="14" ht="31" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>異常時に停止判断を下す権限者</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>氏名の記入が未了（担当は確定済み。管理責任者の記入待ち）</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="15" ht="31" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>文書作成</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>篠原、大塚、茂木（絵）、竹渕（リーダー 茂木（絵）・スケジュール管理担当）</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>同チーム内で調整</t>
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>人名と割り当ては 2026-10-14、篠原のグループによる本人確認で確定。会議記録 §12 の「副管理責任者を倉林さんとし」は本確認と食い違うため、本確認を正とする。</t>
         </is>
       </c>
-      <c r="B17" s="13" t="n"/>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
-      <c r="E17" s="13" t="n"/>
-      <c r="F17" s="13" t="n"/>
-      <c r="G17" s="14" t="n"/>
-    </row>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="16" t="n"/>
+    </row>
+    <row r="18"/>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="14" t="inlineStr">
         <is>
           <t>5-1. 作業時の制約</t>
         </is>
       </c>
-      <c r="B19" s="13" t="n"/>
-      <c r="C19" s="13" t="n"/>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
-      <c r="F19" s="13" t="n"/>
-      <c r="G19" s="14" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="16" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="31" customHeight="1">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>環境</t>
         </is>
@@ -5258,8 +5548,8 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+    <row r="22" ht="17.5" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
         <is>
           <t>原則</t>
         </is>
@@ -5276,6 +5566,9 @@
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A17:G17"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -5290,8 +5583,8 @@
   <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -5300,15 +5593,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -5321,6 +5616,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -5335,156 +5635,162 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>6. 日常管理(日次点検)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>点検項目が未確定のため、本章は枠のみである。会議資料にも引き継ぎ資料にも LNB の点検項目の記載がなく、現行実施者への聞き取りが済むまで本体は書けない。実施してよい時間帯、所要時間の目安、休日の実施有無はいずれも要確認。</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n"/>
-      <c r="C8" s="13" t="n"/>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="14" t="n"/>
-    </row>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+    </row>
+    <row r="9"/>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>記入のきまり</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="13" t="n"/>
-      <c r="E10" s="13" t="n"/>
-      <c r="F10" s="13" t="n"/>
-      <c r="G10" s="14" t="n"/>
-    </row>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="16" t="n"/>
+    </row>
+    <row r="11"/>
     <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>聞き取りの結果をこの形で埋める。各項目を Step として並べ、1項目ごとに次の6点を書く。</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="14" t="n"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="16" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" t="inlineStr">
         <is>
           <t>書く欄</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>書き方</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" t="inlineStr">
         <is>
           <t>やること</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>何を見るか、どこで見るかを書く</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" t="inlineStr">
         <is>
           <t>操作の種別</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>「読み取りのみ」か「状態を変える」のどちらかを書く。曖昧にしない</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" t="inlineStr">
         <is>
           <t>取り消し可否</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>「状態を変える」のときだけ書く。戻せるなら戻し方も書く</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="18" ht="17.5" customHeight="1">
+      <c r="A18" t="inlineStr">
         <is>
           <t>完了条件</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>数値か画面の状態で書く。「問題なければ」とは書かない</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
+    <row r="19" ht="17.5" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>記録</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>残す値・画面・出力を書く。残さないなら「記録なし」と書く</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="16.5" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+    <row r="20" ht="17.5" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>注意点</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>誤読しやすい表示があれば書く</t>
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>なぜ「問題なければ」と書かないのか</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
-      <c r="C22" s="13" t="n"/>
-      <c r="D22" s="13" t="n"/>
-      <c r="E22" s="13" t="n"/>
-      <c r="F22" s="13" t="n"/>
-      <c r="G22" s="14" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="16" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24" ht="17.5" customHeight="1">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
@@ -5495,8 +5801,8 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+    <row r="25" ht="17.5" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>進め方</t>
         </is>
@@ -5507,132 +5813,138 @@
         </is>
       </c>
     </row>
+    <row r="26"/>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="14" t="inlineStr">
         <is>
           <t>Step 1 LNB接続状態を確認する(候補)</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
-      <c r="C27" s="13" t="n"/>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
-      <c r="F27" s="13" t="n"/>
-      <c r="G27" s="14" t="n"/>
-    </row>
-    <row r="29" ht="16.5" customHeight="1">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="16" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29" ht="17.5" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>確定した点検項目ではない。公式資料に「表示される」と書かれている項目なので、聞き取りの出発点として置く。</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
-      <c r="E29" s="13" t="n"/>
-      <c r="F29" s="13" t="n"/>
-      <c r="G29" s="14" t="n"/>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="16" t="n"/>
+    </row>
+    <row r="30"/>
+    <row r="31" ht="17.5" customHeight="1">
+      <c r="A31" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
+    <row r="32" ht="17.5" customHeight="1">
+      <c r="A32" t="inlineStr">
         <is>
           <t>やること</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>LNB接続状態(無線スキャナーと LNB の接続状態)の表示を確認する</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="16.5" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
+    <row r="33" ht="17.5" customHeight="1">
+      <c r="A33" t="inlineStr">
         <is>
           <t>操作の種別</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>読み取りのみ</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
+    <row r="34" ht="17.5" customHeight="1">
+      <c r="A34" t="inlineStr">
         <is>
           <t>完了条件</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>要確認。正常とみなす表示が分かっていない</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+    <row r="35" ht="17.5" customHeight="1">
+      <c r="A35" t="inlineStr">
         <is>
           <t>記録</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>画面名と表示されていた文言をそのまま書く。「正常」「○」とは書かない</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="43.5" customHeight="1">
-      <c r="A36" s="16" t="inlineStr">
+    <row r="36" ht="17.5" customHeight="1">
+      <c r="A36" t="inlineStr">
         <is>
           <t>注意点</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>出典は PanaCIM-EE 材料照合(サーバー無しタイプ)N7201A670J06 PDF通し19頁(付録A-1)。自社の L1〜L3 に同じ表示があるかは未確認</t>
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>判定基準が決まるまでは、見たものをそのまま書く。○×で記録を始めると、基準を決めたあとに過去の記録が読めなくなる。</t>
         </is>
       </c>
-      <c r="B38" s="13" t="n"/>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
-      <c r="F38" s="13" t="n"/>
-      <c r="G38" s="14" t="n"/>
-    </row>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="16" t="n"/>
+    </row>
+    <row r="39"/>
     <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="14" t="inlineStr">
         <is>
           <t>Step 2 以降</t>
         </is>
       </c>
-      <c r="B40" s="13" t="n"/>
-      <c r="C40" s="13" t="n"/>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
-      <c r="F40" s="13" t="n"/>
-      <c r="G40" s="14" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="16" t="n"/>
+    </row>
+    <row r="41"/>
+    <row r="42" ht="17.5" customHeight="1">
+      <c r="A42" s="17" t="inlineStr">
         <is>
           <t>方針</t>
         </is>
@@ -5655,6 +5967,9 @@
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A10:G10"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -5669,8 +5984,8 @@
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -5679,15 +5994,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>手 順 書</t>
         </is>
       </c>
-      <c r="D1" s="11" t="n"/>
-      <c r="E1" s="11" t="n"/>
-      <c r="F1" s="11" t="n"/>
-      <c r="G1" s="11" t="n"/>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -5700,6 +6017,11 @@
           <t>ZZZ-90000(仮)</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -5714,20 +6036,21 @@
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>7. 定期管理</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n"/>
-      <c r="C6" s="13" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="13" t="n"/>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="14" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="17.5" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>頻度区分</t>
         </is>
@@ -5738,8 +6061,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+    <row r="9" ht="17.5" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>月次の有無</t>
         </is>
@@ -5750,8 +6073,8 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+    <row r="10" ht="17.5" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>順序の制約</t>
         </is>
@@ -5762,21 +6085,23 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>頻度を決めるときの観点(会議で挙がった4点)</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="13" t="n"/>
-      <c r="E12" s="13" t="n"/>
-      <c r="F12" s="13" t="n"/>
-      <c r="G12" s="14" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="16" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14" ht="17.5" customHeight="1">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -5787,8 +6112,8 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+    <row r="15" ht="17.5" customHeight="1">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -5799,8 +6124,8 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+    <row r="16" ht="17.5" customHeight="1">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -5811,8 +6136,8 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="17" ht="17.5" customHeight="1">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -5828,6 +6153,9 @@
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A12:G12"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/LNB管理手順書_草案.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/LNB管理手順書_草案.xlsx
@@ -22,9 +22,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記録と文書管理" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チェックシート(日次)" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チェックシート(月次・異常時)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認事項一覧" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="申し送り(認証情報)" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="引用と部品照合" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="会議課題一覧(一時)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="要確認事項一覧" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="申し送り(認証情報)" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="引用と部品照合" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'改訂履歴'!$1:$4</definedName>
@@ -40,9 +41,10 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="12">'記録と文書管理'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="13">'チェックシート(日次)'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="14">'チェックシート(月次・異常時)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="15">'要確認事項一覧'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="16">'申し送り(認証情報)'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="17">'引用と部品照合'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'会議課題一覧(一時)'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="16">'要確認事項一覧'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="17">'申し送り(認証情報)'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="18">'引用と部品照合'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -51,7 +53,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -111,11 +113,23 @@
     <font>
       <name val="游ゴシック"/>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <strike val="1"/>
+      <color rgb="00808080"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
       <color rgb="00833C00"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -125,6 +139,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
       </patternFill>
     </fill>
     <fill>
@@ -213,7 +232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -245,13 +264,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -852,12 +875,12 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -937,7 +960,7 @@
     </row>
     <row r="15"/>
     <row r="16" ht="17.5" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>ここが埋まっていないことが最大の危険。Pana-CIM と Eg-Pro では、バックアップ障害が2件とも「成否を確認する担当が決まっていなかった」ことで長期化している(Eg-Pro のサブサーバー同期は1年以上、nksv523 は6月から暫定運用のまま)。手順書を作るだけでは同じことが起きる。誰がどこで結果を確認し、失敗時に何をするかまで書くこと。</t>
         </is>
@@ -951,7 +974,7 @@
     </row>
     <row r="17"/>
     <row r="18" ht="16.5" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>LNB の運用: DGS を介した手作業。ジョブを消す前に過去ジョブへエクスポートし、必要時にインポートして戻す。取得目的は特定できていない(慣習として続いている)。検討事項: Pana-CIM で一括取得できないか。保存は Pana-CIM で行う。確認担当: 篠原、大塚、茂木。</t>
         </is>
@@ -1052,12 +1075,12 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -1113,7 +1136,7 @@
     </row>
     <row r="13"/>
     <row r="14" ht="17.5" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>戻せることを確認していないバックアップは、バックアップではない。§8 が埋まったら、戻す試験を一度やってから本章を書く。</t>
         </is>
@@ -1213,7 +1236,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
@@ -1240,12 +1263,12 @@
     </row>
     <row r="11"/>
     <row r="12" ht="17.5" customHeight="1">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>欄</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>記載</t>
         </is>
@@ -1337,7 +1360,7 @@
     </row>
     <row r="20"/>
     <row r="21" ht="16.5" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>会議では、異常時の連絡先と復旧確認の実施条件を確認事項として挙げたまま結論に至っていない。</t>
         </is>
@@ -1365,12 +1388,12 @@
     </row>
     <row r="24"/>
     <row r="25" ht="17.5" customHeight="1">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="17" t="inlineStr">
         <is>
           <t>欄</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>記載</t>
         </is>
@@ -1450,7 +1473,7 @@
     </row>
     <row r="32"/>
     <row r="33" ht="17.5" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>自社とベンダーの境界が決まっていないと、異常時に誰も動かない時間が生まれる。</t>
         </is>
@@ -1553,12 +1576,12 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -1652,12 +1675,12 @@
     </row>
     <row r="17"/>
     <row r="18" ht="17.5" customHeight="1">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -1751,12 +1774,12 @@
     </row>
     <row r="27"/>
     <row r="28" ht="17.5" customHeight="1">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>期日</t>
         </is>
@@ -1788,7 +1811,7 @@
     </row>
     <row r="31"/>
     <row r="32" ht="17.5" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>残り日数から逆算すると、聞き取りを先に片付けないと間に合わない。本書の空欄はすべて聞き取りで埋まるもので、文書作成の作業量ではなく聞き取りの段取りが律速。</t>
         </is>
@@ -1890,7 +1913,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>点検項目が未確定なので、列名は仮である。§6 が埋まった時点で列を確定させる。</t>
         </is>
@@ -1904,7 +1927,7 @@
     </row>
     <row r="9"/>
     <row r="10" ht="31" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>対象システム</t>
         </is>
@@ -1916,7 +1939,7 @@
       </c>
     </row>
     <row r="11" ht="17.5" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>年月</t>
         </is>
@@ -1928,7 +1951,7 @@
       </c>
     </row>
     <row r="12" ht="17.5" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
@@ -1941,37 +1964,37 @@
     </row>
     <row r="13"/>
     <row r="14" ht="17.5" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>日</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="17" t="inlineStr">
         <is>
           <t>L3</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="17" t="inlineStr">
         <is>
           <t>異常の有無</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>確認者</t>
         </is>
@@ -2018,7 +2041,7 @@
     </row>
     <row r="18"/>
     <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>ライン別に列を分けてある。接続先が3つあるので、1つにまとめると、どのラインが異常だったのかが残らない。</t>
         </is>
@@ -2046,7 +2069,7 @@
     </row>
     <row r="22"/>
     <row r="23" ht="71.5" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>各ラインの欄</t>
         </is>
@@ -2058,7 +2081,7 @@
       </c>
     </row>
     <row r="24" ht="44.5" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>異常の有無</t>
         </is>
@@ -2070,7 +2093,7 @@
       </c>
     </row>
     <row r="25" ht="71.5" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>原則</t>
         </is>
@@ -2171,7 +2194,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>LNB に月次の作業があるかが未確認。枠だけ置く。</t>
         </is>
@@ -2185,27 +2208,27 @@
     </row>
     <row r="9"/>
     <row r="10" ht="17.5" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>確認項目</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>同席者</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="17" t="inlineStr">
         <is>
           <t>結果</t>
         </is>
@@ -2235,7 +2258,7 @@
     </row>
     <row r="13"/>
     <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Pana-CIM と同日に実施する場合は、順序を記録すること。LNB は Pana-CIM のデータを参照しているため、どちらを先に触ったかが後で問題になる。</t>
         </is>
@@ -2263,37 +2286,37 @@
     </row>
     <row r="17"/>
     <row r="18" ht="17.5" customHeight="1">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>時刻</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>ライン</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="17" t="inlineStr">
         <is>
           <t>画面・文言</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="17" t="inlineStr">
         <is>
           <t>接続状態</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="17" t="inlineStr">
         <is>
           <t>中断内容</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>連絡先/時刻</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="17" t="inlineStr">
         <is>
           <t>記録No.</t>
         </is>
@@ -2319,7 +2342,7 @@
     </row>
     <row r="21"/>
     <row r="22" ht="16.5" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>画面に出ていた文言をそのまま書く。言い換えると、同じ事象かどうかが後で判定できない。</t>
         </is>
@@ -2347,7 +2370,7 @@
     </row>
     <row r="25"/>
     <row r="26" ht="17.5" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>いずれも承認が要る。承認者の記入が無い行は、実施していないものとして扱う。</t>
         </is>
@@ -2361,32 +2384,32 @@
     </row>
     <row r="27"/>
     <row r="28" ht="17.5" customHeight="1">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>実施日</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>対象ライン</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="17" t="inlineStr">
         <is>
           <t>承認者</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="17" t="inlineStr">
         <is>
           <t>実施者</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>結果・記録No.</t>
         </is>
@@ -2444,7 +2467,7 @@
     </row>
     <row r="34"/>
     <row r="35" ht="16.5" customHeight="1">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>点検文書ではないが、§14 を消していくための欄として内包する。聞き取りは一度で終わらない。誰にいつ何を聞いたかが残っていないと、同じことを二度聞くか、聞いたつもりで抜ける。</t>
         </is>
@@ -2458,27 +2481,27 @@
     </row>
     <row r="36"/>
     <row r="37" ht="17.5" customHeight="1">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>確認した欄</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="17" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="17" t="inlineStr">
         <is>
           <t>確認日</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>確認した内容</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="17" t="inlineStr">
         <is>
           <t>記入者</t>
         </is>
@@ -2524,7 +2547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2574,14 +2597,14 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>要確認事項一覧</t>
+          <t>会議課題一覧(一時)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>14. 要確認事項一覧</t>
+          <t>会議で上がった課題の一覧(一時掲載)</t>
         </is>
       </c>
       <c r="B6" s="15" t="n"/>
@@ -2593,9 +2616,9 @@
     </row>
     <row r="7"/>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
-        <is>
-          <t>記入シートの M(未充足一覧)と対応する。埋まったらシート側にも日付を入れる。</t>
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>本シートは会議の場での一覧性を確保するための一時掲載。正本は各管理書(md)の該当章であり、解決後は正本側を更新する。達成度の目安: 反映済み=文書に入った(実機確認や決定が残る)/草案あり=持ち寄り案・骨格まで作成済み(会議の判断で確定)/着手=一部作成/未着手・未決=作業または決定がまだ。</t>
         </is>
       </c>
       <c r="B8" s="15" t="n"/>
@@ -2606,23 +2629,759 @@
       <c r="G8" s="16" t="n"/>
     </row>
     <row r="9"/>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>A. 9-30 会議で挙がった課題12件の達成度</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="16" t="n"/>
+    </row>
+    <row r="11"/>
+    <row r="12" ht="17.5" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>課題</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>達成度</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>現状と残務</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>月次再起動手順</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>管理書 §7 に実手順ベースで記載(SMT点検日の朝・Pana-CIM停止確認)。チェックシートに月次必須項目あり。残務: LNB 側は月次作業の有無自体が未確認(LNB管理書 §14 No.27)。確認方法: 篠原が現行実施者に聞き取り</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44.5" customHeight="1">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>draw.io 相関図 第一層</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>草案あり</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>会議要件どおりの作り直し案を完成(箱6+境界2・線4本)。既存 drawio は業務フロー図のため第一層には使わない。残務: 会議で DGS の位置づけと各箱の管理担当を確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44.5" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>バックアップ(周期・保存)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>管理書 §8 に「周期は毎日・DGSで取得し Pana-CIM で保存」を明記。日次点検 Step 2 で成否確認。残務: 成否の確認者が未決(§8 で最も重要)。戻す試験は未実施(⑫)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44.5" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>④</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>トラブルシューティング</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>反映済み</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>管理書 §10-1 に事象2件(アンドン異常/稼働モニタ異常(Power BI))→再起動手順、正常画面(TrueCase)併記の方針を追記。残務: 画像14枚のうち13枚の対応付け、色定義、記録フォームの所在</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44.5" customHeight="1">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>⑤</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>チェックシートの有無</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>草案あり</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>「あり」で確定(管理手順書に内包)。三項目(稼働状態/バックアップ結果/保存領域)の判定基準案を作成済み。残務: しきい値を実機画面で決定。記録の確認者</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>⑥</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LNB の点検項目</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LNB管理書 §6 は枠のみ。公式資料に書かれた「LNB接続状態」を聞き取りの出発点として Step 1 に準備済み。項目名すら定まっていない(会議記録 §7)。聞き取りは篠原が実施。本会議で日程を決めること(ネック)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>⑦</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>バックアップのデータ確認(誰が・いつ・どこに)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>L1/L2/L3 それぞれで取得していることは会議で確認済み(会議記録 §5)。各ラインで誰が・いつ・どこに保存しているかが必要。確認の材料として LNB_Collector による現場収集(§5)を準備済み。確認先の候補挙げは篠原が実施</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44.5" customHeight="1">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>⑧</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LNB と DGS の中身の確認・関連性整理</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>未着手</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DGS は管理書 §3 用語で「位置づけは要確認」のまま。相関図草案(箱6)でも DGS の管理範囲は「要確認(境界候補)」。調査・整理は篠原が実施し、判定は本会議で。相関図②確定の前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44.5" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>⑨</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>異常時の連絡先と停止判断者</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>未決</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>役割の行は管理書 §5/LNB管理書 §5 にあり、停止判断者の担当は確定済みだが氏名が空欄。管理責任者の記入待ち(会議記録 §10「本人が担当。後日記入」)。文書側の受け皿は完成済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="31" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>⑩</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>管理手順書の草案作成</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>着手</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Pana-CIM v0.11(骨格完成)/LNB v0.9(骨格のみ)。残務: v0.5 相当(基準反映版)は11月中</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>⑪</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>認証情報の保管先</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>未決</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LNB 接続 URL 3件に利用者名とパスワードが平文で埋め込まれていることを確認(LNB管理書 §15)。本文に書かない方針は確定済みだが、書かない前提の「安全な保管先」が存在しないため、§4-2・§15 の参照先が決められない</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>⑫</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>復旧(戻す試験)</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>未実施</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>管理書 §9 は実施条件・頻度とも要確認のまま。取得できていても戻せるかは別であり(管理書 §9)、試験をしないとバックアップの有効性が未証明。実施条件と頻度の案を持ち寄り済み。本会議で確定すること</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>B. 10-14 会議(13:10)で決定を求める9点</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="16" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28" ht="17.5" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>決定事項</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>内容と背景</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="31" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>実機確認の日程</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>最優先。しきい値(正常画面名・色定義・遡り日数・容量)、画像13枚の対応付け、バックアップ保存先の実物確認を1回の訪問で済ませたい</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17.5" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LNB 聞き取りの担当と日程</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>最優先。全体のネック。ここが進まないと LNB 管理書は空白のままで、12月の登録に間に合わない</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="17.5" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>バックアップ成否の確認者</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>管理書 §8 で最も重要</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17.5" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>異常時の連絡先と停止判断者の氏名記入</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>文書側の受け皿は完成済み。管理責任者の記入待ち</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17.5" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>認証情報の保管先</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>保管先を決めれば文書側は記載できる。現状は LNB 接続 URL に平文埋め込み</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17.5" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>復旧(戻す試験)の実施条件と頻度</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>案を持ち寄り済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17.5" customHeight="1">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Windows 更新後の扱い</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>RPA 機と同じ「更新の翌日に再起動」にするか</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17.5" customHeight="1">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>随時再起動の記入欄の可否</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>チェックシートへの記入欄を追加できるか</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17.5" customHeight="1">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LNB と DGS の中身確認の担当</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>持ち帰りタスクで未定になっている分。相関図確定の前提</t>
+        </is>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>C. 解決済みの項目(取り消し線で残す運用の掲載分)</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="16" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41" ht="17.5" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>書</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>項目</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>解決日と内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="31" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>Pana-CIM</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>CIMC-SV の位置づけ</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-05 解決。VMware 上の仮想マシン(RHEL 6・64ビット)。ESXiホスト 172.25.253.45 上で動く。CIM-A PC・CIM-C PC は物理PC</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="44.5" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>Pana-CIM</t>
+        </is>
+      </c>
+      <c r="B43" s="18" t="inlineStr">
+        <is>
+          <t>No.1(一部)</t>
+        </is>
+      </c>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>再起動手順の原本</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-13 解決。操作手順書 0494-912039(06)「PanaCIM」シートに異常時再起動14手順を確認し、原文との突合で完全性を立証済み(管理書 §10-4 突合表)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>Pana-CIM</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>人名・割り当ての確認</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 解決。管理責任者＝茂木（由）・倉林、副管理責任者＝石井・茂木（絵）と確定(本人確認)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="44.5" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>LNB</t>
+        </is>
+      </c>
+      <c r="B45" s="18" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>稼働率フォルダの中身の確認</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 解決。稼働率フォルダにはラインごとの稼働率データ(Pana-CIM 出力の HTML・20260814-1L.htm)が保存されていることを実物で確認。大塚さんへの確認依頼は取り下げ</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="17.5" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
+        <is>
+          <t>LNB</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>人名・割り当ての確認</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 解決。Pana-CIM 側 No.27 と同じ内容(§5)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A10:G10"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>手 順 書</t>
+        </is>
+      </c>
+      <c r="B1" s="12" t="n"/>
+      <c r="C1" s="12" t="n"/>
+      <c r="D1" s="12" t="n"/>
+      <c r="E1" s="12" t="n"/>
+      <c r="F1" s="12" t="n"/>
+      <c r="G1" s="12" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>型   名</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>ZZZ-90000(仮)</t>
+        </is>
+      </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>目次へ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>作業内容</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>要確認事項一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>14. 要確認事項一覧</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="16" t="n"/>
+    </row>
+    <row r="7"/>
+    <row r="8" ht="16.5" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>記入シートの M(未充足一覧)と対応する。埋まったらシート側にも日付を入れる。</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="16" t="n"/>
+    </row>
+    <row r="9"/>
     <row r="10" ht="17.5" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
@@ -3243,6 +4002,226 @@
       <c r="D39" t="inlineStr">
         <is>
           <t>現行実施者、ベンダー</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="44.5" customHeight="1">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>再起動2種の使い分け</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-10-14 実機確認で、LWS の再起動ページに「LNB再起動」「LNB-PC電源OFF」「LNB-PCリブート」の3ボタンがあることを確認。再起動としての2種の対応付け(LNB再起動＝LNBシステム／LNB-PCリブート＝PC自体)はボタン名からの推定【要確認】。実施条件・手順・影響範囲・どちらを選ぶかの判断基準は未確定(§7-1)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>現行実施者、ベンダー</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="31" customHeight="1">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>設定情報の自動バックアップの有効化</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-10-14 実機確認で機能の存在を確認。ただし現在は実行されていない。有効化するか、DGS 経由の手作業に寄せるかを決める(§8)。有効化する場合は成否の確認者を同時に決める</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>管理責任者、ベンダー</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="44.5" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>稼働率フォルダの中身の確認</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 解決。稼働率フォルダには、ラインごとの稼働率データ(Pana-CIM 出力の HTML・20260814-1L.htm)が保存されていることを実物で確認。期間・ロット一覧・仕損率[PPM]・1〜7台目の稼働情報(稼働率・稼働時間・総停止時間)を含む。LNB 側に残せない情報を外部保存している実態とみなせる(§8)。残る確認は保存作業の実施者と自動/手動の別(§8 明細表)</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>実物確認(篠原)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="17.5" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Pana-CIM のバックアップ</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Pana-CIM のバックアップは調査段階にあり、不明な状態。管理書(Pana-CIM 側)§8 とあわせて進める</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>作成チーム、現行実施者</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="31" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>L1 生産設備構成の L2/L3 版</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LWS の LNB構成情報画面で L1 は確認済み(L1NPM-1〜7・SP70-1)。L2/L3 の同画面は未確認。各ラインの設備一覧・IP・バージョンを確認する(§4-3a)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>現行実施者</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="31" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>生産設備番号と IP の対応</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>L1 では番号と IP の末尾が一致しない(番号1＝192.168.21.244 等)。対応表を正式な資料として確定するか、画面で都度確認するかを決める(§4-3a)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>現行実施者</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="31" customHeight="1">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>基板バーコードスキャナの赤表示</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>L1 の Pingチェックで 192.168.0.1 の3項目が赤表示(2026-10-14 撮影時点)。赤が異常を意味するか、恒常的な状態か。赤のまま運用してよいか</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>現行実施者</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="17.5" customHeight="1">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LNB-PC電源OFFの扱い</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>LWS に「LNB-PC電源OFF」ボタンが存在。押してよい場面・押してはいけない場面、実行後の起動手順を確定する(§7-1)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>現行実施者、ベンダー</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="17.5" customHeight="1">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LWS の認証ID</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LNB構成情報画面に「認証ID」の表示がある。値は本書に書かない(§15 と同じ扱い)。管理方法の確定は §15 とあわせて行う</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>管理責任者</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="44.5" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>人名・割り当ての確認</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="inlineStr">
+        <is>
+          <t>2026-10-14 解決。同名は茂木（絵）＝絵美さん（当グループ・スケジュール管理担当）／茂木（由）＝由美子さん（相手グループ）。管理責任者＝茂木（由）・倉林、副管理責任者＝石井・茂木（絵）と確定（§5）。会議記録 §12 の「副管理責任者を倉林さんとし」は本確定と食い違うため、本確定を正とする</t>
+        </is>
+      </c>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>篠原のグループによる本人確認</t>
         </is>
       </c>
     </row>
@@ -3259,7 +4238,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3334,7 +4313,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>本書の作成中に、放置できない状態が見つかった。LNB の接続用ショートカット3件に、利用者名とパスワードが URL のクエリとして平文で埋め込まれている。置き場は 11_USBミラー_E/buckup/15575/desktop/ の L1_LNB.url L2_LNB.url L3_LNB.url。値は本書に書かない。</t>
         </is>
@@ -3348,12 +4327,12 @@
     </row>
     <row r="9"/>
     <row r="10" ht="17.5" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>事実</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>なぜ問題か</t>
         </is>
@@ -3423,7 +4402,7 @@
     </row>
     <row r="17"/>
     <row r="18" ht="17.5" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -3435,7 +4414,7 @@
       </c>
     </row>
     <row r="19" ht="17.5" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3447,7 +4426,7 @@
       </c>
     </row>
     <row r="20" ht="17.5" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -3459,7 +4438,7 @@
       </c>
     </row>
     <row r="21" ht="17.5" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -3472,7 +4451,7 @@
     </row>
     <row r="22"/>
     <row r="23" ht="16.5" customHeight="1">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>こちらの判断で消していない。現物を消すと、現場でその経路しか知らない人が入れなくなる可能性がある。rules.md の削除は承認が必要という扱いにも合わせた。</t>
         </is>
@@ -3499,7 +4478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3574,7 +4553,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="16.5" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>点検項目ではない。設定の前提として記録しておく。公式資料の記載(付録A-2): 無線スキャナーで部品照合機能を使用するには、LNB設定の部品照合設定を行う必要があります。</t>
         </is>
@@ -3588,7 +4567,7 @@
     </row>
     <row r="9"/>
     <row r="10" ht="17.5" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>未確認</t>
         </is>
@@ -3615,7 +4594,7 @@
     </row>
     <row r="13"/>
     <row r="14" ht="16.5" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>改変せずに載せる。本文は読みやすさのために整えてあるので、食い違いがあれば本付録を正とする。</t>
         </is>
@@ -3643,7 +4622,7 @@
     </row>
     <row r="17"/>
     <row r="18" ht="17.5" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>原文</t>
         </is>
@@ -3670,7 +4649,7 @@
     </row>
     <row r="21"/>
     <row r="22" ht="17.5" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>原文</t>
         </is>
@@ -3683,7 +4662,7 @@
     </row>
     <row r="23"/>
     <row r="24" ht="16.5" customHeight="1">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>上記は製品資料の引用であり、自社 L1〜L3 への適用、設定状態、点検項目を確定するものではない。</t>
         </is>
@@ -3711,7 +4690,7 @@
     </row>
     <row r="27"/>
     <row r="28" ht="17.5" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>原文</t>
         </is>
@@ -3723,7 +4702,7 @@
       </c>
     </row>
     <row r="29" ht="17.5" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>限界</t>
         </is>
@@ -3750,7 +4729,7 @@
     </row>
     <row r="32"/>
     <row r="33" ht="17.5" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>確認したもの</t>
         </is>
@@ -3762,7 +4741,7 @@
       </c>
     </row>
     <row r="34" ht="17.5" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>原則</t>
         </is>
@@ -3774,7 +4753,7 @@
       </c>
     </row>
     <row r="35" ht="17.5" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>確認できていないもの</t>
         </is>
@@ -3811,7 +4790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4008,7 +4987,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>要確認事項一覧</t>
+          <t>会議課題一覧(一時)</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4999,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>申し送り(認証情報)</t>
+          <t>要確認事項一覧</t>
         </is>
       </c>
     </row>
@@ -4031,6 +5010,18 @@
         </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>申し送り(認証情報)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>16.</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>引用と部品照合</t>
         </is>
@@ -4053,6 +5044,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4133,27 +5125,27 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>版</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>改訂内容</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>作成</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
@@ -4295,27 +5287,27 @@
       </c>
     </row>
     <row r="14" ht="44.5" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>人名・割り当てを本人確認により確定。§5 を改訂（管理責任者＝茂木（由）・倉林の2名体制、副管理責任者＝石井・茂木（絵））。茂木（絵）のスケジュール管理担当を明記。§14 No.39 解決</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>未</t>
         </is>
@@ -4349,54 +5341,54 @@
       </c>
     </row>
     <row r="16" ht="44.5" customHeight="1">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>0.8</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>稼働率フォルダの中身を実物（20260814-1L.htm）で確認。ラインごとの稼働率データ（期間・ロット一覧・仕損率・1〜7台目の稼働情報）であることを確定し、「LNB では保持できない情報」の根拠に据えた。大塚さんへの確認依頼を取り下げ（§14 No.32 解決）</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>未</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44.5" customHeight="1">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>報告準備。§4-4 に図の読み方（種別ラベル・凡例）と PLM 閲覧問題の現状（大塚さん対応中・解決後に図解を拡充）を追記。構成図に種別ラベル・凡例・稼働率フォルダ（実物確認済み）を反映し視認性を改善</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>篠原</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>未</t>
         </is>
@@ -4489,7 +5481,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -4516,7 +5508,7 @@
     </row>
     <row r="11"/>
     <row r="12" ht="17.5" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>対象</t>
         </is>
@@ -4528,7 +5520,7 @@
       </c>
     </row>
     <row r="13" ht="17.5" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>分冊</t>
         </is>
@@ -4540,7 +5532,7 @@
       </c>
     </row>
     <row r="14" ht="17.5" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>分担</t>
         </is>
@@ -4552,7 +5544,7 @@
       </c>
     </row>
     <row r="15" ht="17.5" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>環境</t>
         </is>
@@ -4564,7 +5556,7 @@
       </c>
     </row>
     <row r="16" ht="17.5" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>未検証</t>
         </is>
@@ -4591,7 +5583,7 @@
     </row>
     <row r="19"/>
     <row r="20" ht="16.5" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>詳細は「LNB・Pana-CIM_管理文書作成_会議記録_追補.md」を参照。本章には経緯の詳細を書かない。</t>
         </is>
@@ -4605,7 +5597,7 @@
     </row>
     <row r="21"/>
     <row r="22" ht="17.5" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>経緯</t>
         </is>
@@ -4617,7 +5609,7 @@
       </c>
     </row>
     <row r="23" ht="17.5" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>教訓</t>
         </is>
@@ -4630,7 +5622,7 @@
     </row>
     <row r="24"/>
     <row r="25" ht="16.5" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>本書は LNB_点検文書_情報記入シート.md の記入済み範囲だけで組んだ草案である。同シートの F(点検項目)は全行が空欄。点検の基準を推測で埋めていない。判定基準を創作すると、異常を正常と読む文書になる。</t>
         </is>
@@ -4733,12 +5725,12 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>語</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>意味</t>
         </is>
@@ -4951,12 +5943,12 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -5062,7 +6054,7 @@
     </row>
     <row r="18"/>
     <row r="19" ht="16.5" customHeight="1">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>保管庫内の資料から確認できた範囲。11_USBミラー_E に残っていたデスクトップのショートカット3件(L1_LNB.url L2_LNB.url L3_LNB.url)から読み取った。</t>
         </is>
@@ -5076,17 +6068,17 @@
     </row>
     <row r="20"/>
     <row r="21" ht="17.5" customHeight="1">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>ライン</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>接続先</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>画面</t>
         </is>
@@ -5145,7 +6137,7 @@
     </row>
     <row r="25"/>
     <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>第4オクテットが 11/21/31 と並んでおり、ラインごとに10ずつ繰り上がる付番と見える。L4以降が存在するかは要確認。</t>
         </is>
@@ -5159,12 +6151,12 @@
     </row>
     <row r="27"/>
     <row r="28" ht="17.5" customHeight="1">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -5258,7 +6250,7 @@
     </row>
     <row r="37"/>
     <row r="38" ht="31" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>参照</t>
         </is>
@@ -5270,7 +6262,7 @@
       </c>
     </row>
     <row r="39" ht="31" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>更新方針</t>
         </is>
@@ -5372,17 +6364,17 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>役割</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>不在時の代行</t>
         </is>
@@ -5509,7 +6501,7 @@
     </row>
     <row r="16"/>
     <row r="17" ht="16.5" customHeight="1">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>人名と割り当ては 2026-10-14、篠原のグループによる本人確認で確定。会議記録 §12 の「副管理責任者を倉林さんとし」は本確認と食い違うため、本確認を正とする。</t>
         </is>
@@ -5537,7 +6529,7 @@
     </row>
     <row r="20"/>
     <row r="21" ht="31" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>環境</t>
         </is>
@@ -5549,7 +6541,7 @@
       </c>
     </row>
     <row r="22" ht="17.5" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>原則</t>
         </is>
@@ -5649,7 +6641,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>点検項目が未確定のため、本章は枠のみである。会議資料にも引き継ぎ資料にも LNB の点検項目の記載がなく、現行実施者への聞き取りが済むまで本体は書けない。実施してよい時間帯、所要時間の目安、休日の実施有無はいずれも要確認。</t>
         </is>
@@ -5677,7 +6669,7 @@
     </row>
     <row r="11"/>
     <row r="12" ht="16.5" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>聞き取りの結果をこの形で埋める。各項目を Step として並べ、1項目ごとに次の6点を書く。</t>
         </is>
@@ -5691,12 +6683,12 @@
     </row>
     <row r="13"/>
     <row r="14" ht="17.5" customHeight="1">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>書く欄</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>書き方</t>
         </is>
@@ -5790,7 +6782,7 @@
     </row>
     <row r="23"/>
     <row r="24" ht="17.5" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>理由</t>
         </is>
@@ -5802,7 +6794,7 @@
       </c>
     </row>
     <row r="25" ht="17.5" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>進め方</t>
         </is>
@@ -5829,7 +6821,7 @@
     </row>
     <row r="28"/>
     <row r="29" ht="17.5" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>確定した点検項目ではない。公式資料に「表示される」と書かれている項目なので、聞き取りの出発点として置く。</t>
         </is>
@@ -5843,12 +6835,12 @@
     </row>
     <row r="30"/>
     <row r="31" ht="17.5" customHeight="1">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>項目</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="17" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
@@ -5916,7 +6908,7 @@
     </row>
     <row r="37"/>
     <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>判定基準が決まるまでは、見たものをそのまま書く。○×で記録を始めると、基準を決めたあとに過去の記録が読めなくなる。</t>
         </is>
@@ -5944,7 +6936,7 @@
     </row>
     <row r="41"/>
     <row r="42" ht="17.5" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>方針</t>
         </is>
@@ -6050,7 +7042,7 @@
     </row>
     <row r="7"/>
     <row r="8" ht="17.5" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>頻度区分</t>
         </is>
@@ -6062,7 +7054,7 @@
       </c>
     </row>
     <row r="9" ht="17.5" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>月次の有無</t>
         </is>
@@ -6074,7 +7066,7 @@
       </c>
     </row>
     <row r="10" ht="17.5" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>順序の制約</t>
         </is>
@@ -6101,7 +7093,7 @@
     </row>
     <row r="13"/>
     <row r="14" ht="17.5" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -6113,7 +7105,7 @@
       </c>
     </row>
     <row r="15" ht="17.5" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -6125,7 +7117,7 @@
       </c>
     </row>
     <row r="16" ht="17.5" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -6137,7 +7129,7 @@
       </c>
     </row>
     <row r="17" ht="17.5" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>4</t>
         </is>

--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/LNB管理手順書_草案.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/LNB管理手順書_草案.xlsx
@@ -2322,7 +2322,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="17.5" customHeight="1">
+    <row r="19" ht="24" customHeight="1">
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
@@ -2331,7 +2331,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
     </row>
-    <row r="20" ht="17.5" customHeight="1">
+    <row r="20" ht="24" customHeight="1">
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
@@ -2507,14 +2507,14 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="17.5" customHeight="1">
+    <row r="38" ht="24" customHeight="1">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
     </row>
-    <row r="39" ht="17.5" customHeight="1">
+    <row r="39" ht="24" customHeight="1">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>

--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/LNB管理手順書_草案.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/LNB管理手順書_草案.xlsx
@@ -695,7 +695,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>0.9(草案・未検証)</t>
+          <t>0.11(草案・未検証)</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5389,6 +5389,60 @@
         </is>
       </c>
       <c r="E17" s="18" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44.5" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>用語の正式名称を確定（§3）。LNB＝Line Network Box の略（実装設備群と NPM-DGS を接続する中継・ライン管理システム）、DGS＝NPM-DGS（Data Generation System）。LWS 画面タイトルとの整合を明記</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>篠原</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="31" customHeight="1">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0.11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>§3 の LNB 正式名称の出典を訂正。「ユーザー本人の確認」→「竹渕さんのチャット情報」。内容の変更なし（出典の記載のみ）</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>篠原</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
         <is>
           <t>未</t>
         </is>
@@ -5736,7 +5790,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="17.5" customHeight="1">
+    <row r="9" ht="31" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
           <t>LNB</t>
@@ -5744,7 +5798,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>社内での呼び名。本書では、承認済みの L1〜L3 端末と、そこで稼働する LNB ソフトを対象とする。iLNB と同一であるとは断定しない</t>
+          <t>Line Network Box の略。実装設備群と NPM-DGS（Data Generation System）を接続する中継・ライン管理システム（2026-10-14、竹渕さんのチャット情報により確定）。本書では、承認済みの L1〜L3 端末と、そこで稼働する LNB ソフトを対象とする。iLNB と同一であるとは断定しない</t>
         </is>
       </c>
     </row>
@@ -5768,7 +5822,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LNB の画面を提供しているアプリケーションの経路名。接続先URLの /lws/ にあたる。正式な呼称は要確認</t>
+          <t>LNB の画面を提供しているアプリケーションの経路名。接続先URLの /lws/ にあたる。画面タイトル「Line Network Box」は LNB の正式名称確定と整合。正式な呼称は要確認</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5874,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="17.5" customHeight="1">
+    <row r="16" ht="31" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
           <t>DGS</t>
@@ -5828,7 +5882,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LNB のバックアップ経路に現れる系。本書での位置づけは要確認</t>
+          <t>NPM-DGS（Data Generation System）。実装データを生成・管理する上位システム。LNB のバックアップ経路に現れる。LWS の Pingチェック画面では「上位システム」として表示（IP 172.25.253.10）。本書での位置づけは要確認</t>
         </is>
       </c>
     </row>

--- a/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/LNB管理手順書_草案.xlsx
+++ b/workvault-sync/10_業務全般/PanaCIM_LNB/01_成果物/LNB管理手順書_草案.xlsx
@@ -1934,7 +1934,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>LNB</t>
+          <t>LNB(Line Network Box)</t>
         </is>
       </c>
     </row>
